--- a/docs/dla-course-2/downloads/SU_DLA_Solar_Student_Workbook_V8.xlsx
+++ b/docs/dla-course-2/downloads/SU_DLA_Solar_Student_Workbook_V8.xlsx
@@ -1269,8 +1269,10 @@
       <x:c r="F39" s="115"/>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" s="8" t="str">
-        <x:v>Use Microsoft Excel or Google Sheets. Formulas, sheet names and course-critical cell addresses are identical; interface differences are explained on the Google Site.</x:v>
+      <x:c r="A40" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Complete the activity in Microsoft Excel. Google Sheets compatibility instructions are provided on the course site; sheet names and cell addresses remain the same.</x:t>
+        </x:is>
       </x:c>
       <x:c r="B40" s="8"/>
       <x:c r="C40" s="8"/>
@@ -2922,8 +2924,10 @@
       <x:c r="N2" s="41"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="43" t="str">
-        <x:v>The Production Manager challenges System C's 78% self-consumption assumption. Use the Google Site's supplied 20-year NPV formulas in B8:E8, then fill them down through row 14. Your task is to use and interrogate the discounted-cash-flow model, not build the full 20-year engine from first principles.</x:v>
+      <x:c r="A3" s="43" t="inlineStr">
+        <x:is>
+          <x:t>The first sensitivity row B8:E8 is supplied. Inspect the scenario reference $A8 in D8, then fill B8:E8 down through row 14. Refine the crossover by temporarily testing 74% and 73.9% in A14; restore 60% afterwards. Interpret the results rather than transcribing the NPV engine.</x:t>
+        </x:is>
       </x:c>
       <x:c r="B3" s="43"/>
       <x:c r="C3" s="43"/>
@@ -3027,10 +3031,22 @@
       <x:c r="A8" s="111" t="n">
         <x:v>0.78</x:v>
       </x:c>
-      <x:c r="B8" s="107"/>
-      <x:c r="C8" s="107"/>
-      <x:c r="D8" s="107"/>
-      <x:c r="E8" s="81"/>
+      <x:c r="B8" s="107" t="n">
+        <x:f>-'Case Data'!$B$13+(('Case Data'!$B$15*(1-'Case Data'!$B$7)^0*'Case Data'!$B$16*'Case Data'!$B$4*(1+'Case Data'!$B$5)^0-'Case Data'!$B$17*(1+'Case Data'!$B$8)^0)/(1+'Case Data'!$B$6)^1)+(('Case Data'!$B$15*(1-'Case Data'!$B$7)^1*'Case Data'!$B$16*'Case Data'!$B$4*(1+'Case Data'!$B$5)^1-'Case Data'!$B$17*(1+'Case Data'!$B$8)^1)/(1+'Case Data'!$B$6)^2)+(('Case Data'!$B$15*(1-'Case Data'!$B$7)^2*'Case Data'!$B$16*'Case Data'!$B$4*(1+'Case Data'!$B$5)^2-'Case Data'!$B$17*(1+'Case Data'!$B$8)^2)/(1+'Case Data'!$B$6)^3)+(('Case Data'!$B$15*(1-'Case Data'!$B$7)^3*'Case Data'!$B$16*'Case Data'!$B$4*(1+'Case Data'!$B$5)^3-'Case Data'!$B$17*(1+'Case Data'!$B$8)^3)/(1+'Case Data'!$B$6)^4)+(('Case Data'!$B$15*(1-'Case Data'!$B$7)^4*'Case Data'!$B$16*'Case Data'!$B$4*(1+'Case Data'!$B$5)^4-'Case Data'!$B$17*(1+'Case Data'!$B$8)^4)/(1+'Case Data'!$B$6)^5)+(('Case Data'!$B$15*(1-'Case Data'!$B$7)^5*'Case Data'!$B$16*'Case Data'!$B$4*(1+'Case Data'!$B$5)^5-'Case Data'!$B$17*(1+'Case Data'!$B$8)^5)/(1+'Case Data'!$B$6)^6)+(('Case Data'!$B$15*(1-'Case Data'!$B$7)^6*'Case Data'!$B$16*'Case Data'!$B$4*(1+'Case Data'!$B$5)^6-'Case Data'!$B$17*(1+'Case Data'!$B$8)^6)/(1+'Case Data'!$B$6)^7)+(('Case Data'!$B$15*(1-'Case Data'!$B$7)^7*'Case Data'!$B$16*'Case Data'!$B$4*(1+'Case Data'!$B$5)^7-'Case Data'!$B$17*(1+'Case Data'!$B$8)^7)/(1+'Case Data'!$B$6)^8)+(('Case Data'!$B$15*(1-'Case Data'!$B$7)^8*'Case Data'!$B$16*'Case Data'!$B$4*(1+'Case Data'!$B$5)^8-'Case Data'!$B$17*(1+'Case Data'!$B$8)^8)/(1+'Case Data'!$B$6)^9)+(('Case Data'!$B$15*(1-'Case Data'!$B$7)^9*'Case Data'!$B$16*'Case Data'!$B$4*(1+'Case Data'!$B$5)^9-'Case Data'!$B$17*(1+'Case Data'!$B$8)^9)/(1+'Case Data'!$B$6)^10)+(('Case Data'!$B$15*(1-'Case Data'!$B$7)^10*'Case Data'!$B$16*'Case Data'!$B$4*(1+'Case Data'!$B$5)^10-'Case Data'!$B$17*(1+'Case Data'!$B$8)^10)/(1+'Case Data'!$B$6)^11)+(('Case Data'!$B$15*(1-'Case Data'!$B$7)^11*'Case Data'!$B$16*'Case Data'!$B$4*(1+'Case Data'!$B$5)^11-'Case Data'!$B$17*(1+'Case Data'!$B$8)^11)/(1+'Case Data'!$B$6)^12)+(('Case Data'!$B$15*(1-'Case Data'!$B$7)^12*'Case Data'!$B$16*'Case Data'!$B$4*(1+'Case Data'!$B$5)^12-'Case Data'!$B$17*(1+'Case Data'!$B$8)^12)/(1+'Case Data'!$B$6)^13)+(('Case Data'!$B$15*(1-'Case Data'!$B$7)^13*'Case Data'!$B$16*'Case Data'!$B$4*(1+'Case Data'!$B$5)^13-'Case Data'!$B$17*(1+'Case Data'!$B$8)^13)/(1+'Case Data'!$B$6)^14)+(('Case Data'!$B$15*(1-'Case Data'!$B$7)^14*'Case Data'!$B$16*'Case Data'!$B$4*(1+'Case Data'!$B$5)^14-'Case Data'!$B$17*(1+'Case Data'!$B$8)^14)/(1+'Case Data'!$B$6)^15)+(('Case Data'!$B$15*(1-'Case Data'!$B$7)^15*'Case Data'!$B$16*'Case Data'!$B$4*(1+'Case Data'!$B$5)^15-'Case Data'!$B$17*(1+'Case Data'!$B$8)^15)/(1+'Case Data'!$B$6)^16)+(('Case Data'!$B$15*(1-'Case Data'!$B$7)^16*'Case Data'!$B$16*'Case Data'!$B$4*(1+'Case Data'!$B$5)^16-'Case Data'!$B$17*(1+'Case Data'!$B$8)^16)/(1+'Case Data'!$B$6)^17)+(('Case Data'!$B$15*(1-'Case Data'!$B$7)^17*'Case Data'!$B$16*'Case Data'!$B$4*(1+'Case Data'!$B$5)^17-'Case Data'!$B$17*(1+'Case Data'!$B$8)^17)/(1+'Case Data'!$B$6)^18)+(('Case Data'!$B$15*(1-'Case Data'!$B$7)^18*'Case Data'!$B$16*'Case Data'!$B$4*(1+'Case Data'!$B$5)^18-'Case Data'!$B$17*(1+'Case Data'!$B$8)^18)/(1+'Case Data'!$B$6)^19)+(('Case Data'!$B$15*(1-'Case Data'!$B$7)^19*'Case Data'!$B$16*'Case Data'!$B$4*(1+'Case Data'!$B$5)^19-'Case Data'!$B$17*(1+'Case Data'!$B$8)^19)/(1+'Case Data'!$B$6)^20)</x:f>
+        <x:v>2151805.719638207</x:v>
+      </x:c>
+      <x:c r="C8" s="107" t="n">
+        <x:f>-'Case Data'!$C$13+(('Case Data'!$C$15*(1-'Case Data'!$B$7)^0*'Case Data'!$C$16*'Case Data'!$B$4*(1+'Case Data'!$B$5)^0-'Case Data'!$C$17*(1+'Case Data'!$B$8)^0)/(1+'Case Data'!$B$6)^1)+(('Case Data'!$C$15*(1-'Case Data'!$B$7)^1*'Case Data'!$C$16*'Case Data'!$B$4*(1+'Case Data'!$B$5)^1-'Case Data'!$C$17*(1+'Case Data'!$B$8)^1)/(1+'Case Data'!$B$6)^2)+(('Case Data'!$C$15*(1-'Case Data'!$B$7)^2*'Case Data'!$C$16*'Case Data'!$B$4*(1+'Case Data'!$B$5)^2-'Case Data'!$C$17*(1+'Case Data'!$B$8)^2)/(1+'Case Data'!$B$6)^3)+(('Case Data'!$C$15*(1-'Case Data'!$B$7)^3*'Case Data'!$C$16*'Case Data'!$B$4*(1+'Case Data'!$B$5)^3-'Case Data'!$C$17*(1+'Case Data'!$B$8)^3)/(1+'Case Data'!$B$6)^4)+(('Case Data'!$C$15*(1-'Case Data'!$B$7)^4*'Case Data'!$C$16*'Case Data'!$B$4*(1+'Case Data'!$B$5)^4-'Case Data'!$C$17*(1+'Case Data'!$B$8)^4)/(1+'Case Data'!$B$6)^5)+(('Case Data'!$C$15*(1-'Case Data'!$B$7)^5*'Case Data'!$C$16*'Case Data'!$B$4*(1+'Case Data'!$B$5)^5-'Case Data'!$C$17*(1+'Case Data'!$B$8)^5)/(1+'Case Data'!$B$6)^6)+(('Case Data'!$C$15*(1-'Case Data'!$B$7)^6*'Case Data'!$C$16*'Case Data'!$B$4*(1+'Case Data'!$B$5)^6-'Case Data'!$C$17*(1+'Case Data'!$B$8)^6)/(1+'Case Data'!$B$6)^7)+(('Case Data'!$C$15*(1-'Case Data'!$B$7)^7*'Case Data'!$C$16*'Case Data'!$B$4*(1+'Case Data'!$B$5)^7-'Case Data'!$C$17*(1+'Case Data'!$B$8)^7)/(1+'Case Data'!$B$6)^8)+(('Case Data'!$C$15*(1-'Case Data'!$B$7)^8*'Case Data'!$C$16*'Case Data'!$B$4*(1+'Case Data'!$B$5)^8-'Case Data'!$C$17*(1+'Case Data'!$B$8)^8)/(1+'Case Data'!$B$6)^9)+(('Case Data'!$C$15*(1-'Case Data'!$B$7)^9*'Case Data'!$C$16*'Case Data'!$B$4*(1+'Case Data'!$B$5)^9-'Case Data'!$C$17*(1+'Case Data'!$B$8)^9)/(1+'Case Data'!$B$6)^10)+(('Case Data'!$C$15*(1-'Case Data'!$B$7)^10*'Case Data'!$C$16*'Case Data'!$B$4*(1+'Case Data'!$B$5)^10-'Case Data'!$C$17*(1+'Case Data'!$B$8)^10)/(1+'Case Data'!$B$6)^11)+(('Case Data'!$C$15*(1-'Case Data'!$B$7)^11*'Case Data'!$C$16*'Case Data'!$B$4*(1+'Case Data'!$B$5)^11-'Case Data'!$C$17*(1+'Case Data'!$B$8)^11)/(1+'Case Data'!$B$6)^12)+(('Case Data'!$C$15*(1-'Case Data'!$B$7)^12*'Case Data'!$C$16*'Case Data'!$B$4*(1+'Case Data'!$B$5)^12-'Case Data'!$C$17*(1+'Case Data'!$B$8)^12)/(1+'Case Data'!$B$6)^13)+(('Case Data'!$C$15*(1-'Case Data'!$B$7)^13*'Case Data'!$C$16*'Case Data'!$B$4*(1+'Case Data'!$B$5)^13-'Case Data'!$C$17*(1+'Case Data'!$B$8)^13)/(1+'Case Data'!$B$6)^14)+(('Case Data'!$C$15*(1-'Case Data'!$B$7)^14*'Case Data'!$C$16*'Case Data'!$B$4*(1+'Case Data'!$B$5)^14-'Case Data'!$C$17*(1+'Case Data'!$B$8)^14)/(1+'Case Data'!$B$6)^15)+(('Case Data'!$C$15*(1-'Case Data'!$B$7)^15*'Case Data'!$C$16*'Case Data'!$B$4*(1+'Case Data'!$B$5)^15-'Case Data'!$C$17*(1+'Case Data'!$B$8)^15)/(1+'Case Data'!$B$6)^16)+(('Case Data'!$C$15*(1-'Case Data'!$B$7)^16*'Case Data'!$C$16*'Case Data'!$B$4*(1+'Case Data'!$B$5)^16-'Case Data'!$C$17*(1+'Case Data'!$B$8)^16)/(1+'Case Data'!$B$6)^17)+(('Case Data'!$C$15*(1-'Case Data'!$B$7)^17*'Case Data'!$C$16*'Case Data'!$B$4*(1+'Case Data'!$B$5)^17-'Case Data'!$C$17*(1+'Case Data'!$B$8)^17)/(1+'Case Data'!$B$6)^18)+(('Case Data'!$C$15*(1-'Case Data'!$B$7)^18*'Case Data'!$C$16*'Case Data'!$B$4*(1+'Case Data'!$B$5)^18-'Case Data'!$C$17*(1+'Case Data'!$B$8)^18)/(1+'Case Data'!$B$6)^19)+(('Case Data'!$C$15*(1-'Case Data'!$B$7)^19*'Case Data'!$C$16*'Case Data'!$B$4*(1+'Case Data'!$B$5)^19-'Case Data'!$C$17*(1+'Case Data'!$B$8)^19)/(1+'Case Data'!$B$6)^20)</x:f>
+        <x:v>2662434.5738290427</x:v>
+      </x:c>
+      <x:c r="D8" s="107" t="n">
+        <x:f>-'Case Data'!$D$13+(('Case Data'!$D$15*(1-'Case Data'!$B$7)^0*$A8*'Case Data'!$B$4*(1+'Case Data'!$B$5)^0-'Case Data'!$D$17*(1+'Case Data'!$B$8)^0)/(1+'Case Data'!$B$6)^1)+(('Case Data'!$D$15*(1-'Case Data'!$B$7)^1*$A8*'Case Data'!$B$4*(1+'Case Data'!$B$5)^1-'Case Data'!$D$17*(1+'Case Data'!$B$8)^1)/(1+'Case Data'!$B$6)^2)+(('Case Data'!$D$15*(1-'Case Data'!$B$7)^2*$A8*'Case Data'!$B$4*(1+'Case Data'!$B$5)^2-'Case Data'!$D$17*(1+'Case Data'!$B$8)^2)/(1+'Case Data'!$B$6)^3)+(('Case Data'!$D$15*(1-'Case Data'!$B$7)^3*$A8*'Case Data'!$B$4*(1+'Case Data'!$B$5)^3-'Case Data'!$D$17*(1+'Case Data'!$B$8)^3)/(1+'Case Data'!$B$6)^4)+(('Case Data'!$D$15*(1-'Case Data'!$B$7)^4*$A8*'Case Data'!$B$4*(1+'Case Data'!$B$5)^4-'Case Data'!$D$17*(1+'Case Data'!$B$8)^4)/(1+'Case Data'!$B$6)^5)+(('Case Data'!$D$15*(1-'Case Data'!$B$7)^5*$A8*'Case Data'!$B$4*(1+'Case Data'!$B$5)^5-'Case Data'!$D$17*(1+'Case Data'!$B$8)^5)/(1+'Case Data'!$B$6)^6)+(('Case Data'!$D$15*(1-'Case Data'!$B$7)^6*$A8*'Case Data'!$B$4*(1+'Case Data'!$B$5)^6-'Case Data'!$D$17*(1+'Case Data'!$B$8)^6)/(1+'Case Data'!$B$6)^7)+(('Case Data'!$D$15*(1-'Case Data'!$B$7)^7*$A8*'Case Data'!$B$4*(1+'Case Data'!$B$5)^7-'Case Data'!$D$17*(1+'Case Data'!$B$8)^7)/(1+'Case Data'!$B$6)^8)+(('Case Data'!$D$15*(1-'Case Data'!$B$7)^8*$A8*'Case Data'!$B$4*(1+'Case Data'!$B$5)^8-'Case Data'!$D$17*(1+'Case Data'!$B$8)^8)/(1+'Case Data'!$B$6)^9)+(('Case Data'!$D$15*(1-'Case Data'!$B$7)^9*$A8*'Case Data'!$B$4*(1+'Case Data'!$B$5)^9-'Case Data'!$D$17*(1+'Case Data'!$B$8)^9)/(1+'Case Data'!$B$6)^10)+(('Case Data'!$D$15*(1-'Case Data'!$B$7)^10*$A8*'Case Data'!$B$4*(1+'Case Data'!$B$5)^10-'Case Data'!$D$17*(1+'Case Data'!$B$8)^10)/(1+'Case Data'!$B$6)^11)+(('Case Data'!$D$15*(1-'Case Data'!$B$7)^11*$A8*'Case Data'!$B$4*(1+'Case Data'!$B$5)^11-'Case Data'!$D$17*(1+'Case Data'!$B$8)^11)/(1+'Case Data'!$B$6)^12)+(('Case Data'!$D$15*(1-'Case Data'!$B$7)^12*$A8*'Case Data'!$B$4*(1+'Case Data'!$B$5)^12-'Case Data'!$D$17*(1+'Case Data'!$B$8)^12)/(1+'Case Data'!$B$6)^13)+(('Case Data'!$D$15*(1-'Case Data'!$B$7)^13*$A8*'Case Data'!$B$4*(1+'Case Data'!$B$5)^13-'Case Data'!$D$17*(1+'Case Data'!$B$8)^13)/(1+'Case Data'!$B$6)^14)+(('Case Data'!$D$15*(1-'Case Data'!$B$7)^14*$A8*'Case Data'!$B$4*(1+'Case Data'!$B$5)^14-'Case Data'!$D$17*(1+'Case Data'!$B$8)^14)/(1+'Case Data'!$B$6)^15)+(('Case Data'!$D$15*(1-'Case Data'!$B$7)^15*$A8*'Case Data'!$B$4*(1+'Case Data'!$B$5)^15-'Case Data'!$D$17*(1+'Case Data'!$B$8)^15)/(1+'Case Data'!$B$6)^16)+(('Case Data'!$D$15*(1-'Case Data'!$B$7)^16*$A8*'Case Data'!$B$4*(1+'Case Data'!$B$5)^16-'Case Data'!$D$17*(1+'Case Data'!$B$8)^16)/(1+'Case Data'!$B$6)^17)+(('Case Data'!$D$15*(1-'Case Data'!$B$7)^17*$A8*'Case Data'!$B$4*(1+'Case Data'!$B$5)^17-'Case Data'!$D$17*(1+'Case Data'!$B$8)^17)/(1+'Case Data'!$B$6)^18)+(('Case Data'!$D$15*(1-'Case Data'!$B$7)^18*$A8*'Case Data'!$B$4*(1+'Case Data'!$B$5)^18-'Case Data'!$D$17*(1+'Case Data'!$B$8)^18)/(1+'Case Data'!$B$6)^19)+(('Case Data'!$D$15*(1-'Case Data'!$B$7)^19*$A8*'Case Data'!$B$4*(1+'Case Data'!$B$5)^19-'Case Data'!$D$17*(1+'Case Data'!$B$8)^19)/(1+'Case Data'!$B$6)^20)</x:f>
+        <x:v>2871276.0869148397</x:v>
+      </x:c>
+      <x:c r="E8" s="81" t="str">
+        <x:f>CHOOSE(MATCH(MAX(B8:D8),B8:D8,0),"A","B","C")</x:f>
+        <x:v>C</x:v>
+      </x:c>
       <x:c r="F8" s="43"/>
       <x:c r="G8" s="43"/>
       <x:c r="H8" s="43"/>
@@ -3312,8 +3328,10 @@
       <x:c r="N23" s="41"/>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="43" t="str">
-        <x:v>Use the Google Site formulas exactly as printed in either Excel or Google Sheets. SUMPRODUCT, ROW, MAX, MATCH, CHOOSE, absolute references and mixed references are used identically in this activity.</x:v>
+      <x:c r="A24" s="43" t="inlineStr">
+        <x:is>
+          <x:t>Microsoft Excel: use the fill handle to copy B8:E8 down to row 14. Google Sheets compatibility: select B8:E14 and use Fill down. The supplied NPV engine uses a fixed 20-year horizon and year-end cash flows.</x:t>
+        </x:is>
       </x:c>
       <x:c r="B24" s="43"/>
       <x:c r="C24" s="43"/>
@@ -4081,8 +4099,10 @@
       <x:c r="N28" s="41"/>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" s="102" t="str">
-        <x:v>Why can the shortest payback and the highest NPV point to different proposals?</x:v>
+      <x:c r="A29" s="102" t="inlineStr">
+        <x:is>
+          <x:t>Revisit: What did you initially think mattered most in choosing between the proposals?</x:t>
+        </x:is>
       </x:c>
       <x:c r="B29" s="102"/>
       <x:c r="C29" s="102"/>
@@ -4099,8 +4119,10 @@
       <x:c r="N29" s="41"/>
     </x:row>
     <x:row r="30">
-      <x:c r="A30" s="102" t="str">
-        <x:v>Which assumption carries the highest financial risk in this case, and what evidence would you obtain?</x:v>
+      <x:c r="A30" s="102" t="inlineStr">
+        <x:is>
+          <x:t>Explain: Which result, assumption or sensitivity finding changed or strengthened your judgement, and why?</x:t>
+        </x:is>
       </x:c>
       <x:c r="B30" s="102"/>
       <x:c r="C30" s="102"/>
@@ -4117,8 +4139,10 @@
       <x:c r="N30" s="41"/>
     </x:row>
     <x:row r="31">
-      <x:c r="A31" s="102" t="str">
-        <x:v>How does this modelling pattern transfer to another capital-allocation problem?</x:v>
+      <x:c r="A31" s="102" t="inlineStr">
+        <x:is>
+          <x:t>Transfer: Identify another business investment decision where this analytical pattern could be used.</x:t>
+        </x:is>
       </x:c>
       <x:c r="B31" s="102"/>
       <x:c r="C31" s="102"/>
@@ -4151,8 +4175,10 @@
       <x:c r="N32" s="41"/>
     </x:row>
     <x:row r="33">
-      <x:c r="A33" s="102" t="str">
-        <x:v>Transfer pattern: Inputs → assumptions → calculation → alternatives → sensitivity → evidence → recommendation</x:v>
+      <x:c r="A33" s="102" t="inlineStr">
+        <x:is>
+          <x:t>Transfer pattern: Inputs → Model → Test assumptions → Interpret → Recommend</x:t>
+        </x:is>
       </x:c>
       <x:c r="B33" s="102"/>
       <x:c r="C33" s="102"/>
